--- a/reports/cpu_int8/summary_results.xlsx
+++ b/reports/cpu_int8/summary_results.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -597,37 +597,37 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7.919425487518311</v>
+        <v>60.36861348152161</v>
       </c>
       <c r="K2" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="P2" t="n">
-        <v>1.11392816382589</v>
+        <v>3.577812784336889</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.331245740935037</v>
+        <v>62.19613654096213</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2981121217024075</v>
+        <v>0.197666785538512</v>
       </c>
       <c r="S2" t="n">
-        <v>4.743286026463334</v>
+        <v>65.97161611083753</v>
       </c>
       <c r="T2" t="n">
-        <v>210.824309228009</v>
+        <v>15.15803399934786</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -661,7 +661,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -694,37 +694,37 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9.623297214508057</v>
+        <v>60.18165683746338</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="P3" t="n">
-        <v>1.253191286763555</v>
+        <v>3.389318269883992</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.189332919293476</v>
+        <v>62.37194781927823</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3370381445877804</v>
+        <v>0.1931943999960526</v>
       </c>
       <c r="S3" t="n">
-        <v>5.779562350644812</v>
+        <v>65.95446048915828</v>
       </c>
       <c r="T3" t="n">
-        <v>173.023481594317</v>
+        <v>15.16197680313649</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -791,37 +791,37 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8.807447671890259</v>
+        <v>61.96895003318787</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="P4" t="n">
-        <v>1.218224668658636</v>
+        <v>3.411678866263152</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.698993178317411</v>
+        <v>63.74046757107902</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3291073975779877</v>
+        <v>0.1977146614480952</v>
       </c>
       <c r="S4" t="n">
-        <v>5.246325244554034</v>
+        <v>67.34986109879026</v>
       </c>
       <c r="T4" t="n">
-        <v>190.6096083230931</v>
+        <v>14.84784056990375</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -888,37 +888,37 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9.109304189682007</v>
+        <v>61.25183415412903</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="P5" t="n">
-        <v>1.178099043370668</v>
+        <v>2.823422363845917</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.615107284318824</v>
+        <v>61.99228953855325</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3302919927525828</v>
+        <v>0.1924064445750238</v>
       </c>
       <c r="S5" t="n">
-        <v>5.123498320442075</v>
+        <v>65.0081183469742</v>
       </c>
       <c r="T5" t="n">
-        <v>195.1791407855319</v>
+        <v>15.38269412233411</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -952,7 +952,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -985,37 +985,37 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9.767948627471924</v>
+        <v>60.29372668266296</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="P6" t="n">
-        <v>1.251274537317369</v>
+        <v>3.255934819278454</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.304716331348737</v>
+        <v>62.35827147952231</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3350898818755824</v>
+        <v>0.1926298638485912</v>
       </c>
       <c r="S6" t="n">
-        <v>5.891080750541688</v>
+        <v>65.80683616264936</v>
       </c>
       <c r="T6" t="n">
-        <v>169.7481400009751</v>
+        <v>15.19598963135657</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1082,37 +1082,37 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>8.508018255233765</v>
+        <v>61.55682325363159</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="P7" t="n">
-        <v>1.166719560232119</v>
+        <v>3.363454225299151</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.455434873495801</v>
+        <v>63.5377552445712</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3199979036417719</v>
+        <v>0.1923058012109147</v>
       </c>
       <c r="S7" t="n">
-        <v>4.942152337369691</v>
+        <v>67.09351527108127</v>
       </c>
       <c r="T7" t="n">
-        <v>202.3409906729462</v>
+        <v>14.90457007595518</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1179,37 +1179,37 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>9.51214861869812</v>
+        <v>62.94834685325623</v>
       </c>
       <c r="K8" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="P8" t="n">
-        <v>1.261353527777565</v>
+        <v>3.201961490365548</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.083493655442393</v>
+        <v>63.81637453132169</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3286296807499343</v>
+        <v>0.194701428919476</v>
       </c>
       <c r="S8" t="n">
-        <v>5.673476863969892</v>
+        <v>67.21303745060672</v>
       </c>
       <c r="T8" t="n">
-        <v>176.258760540758</v>
+        <v>14.87806589212512</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1276,37 +1276,37 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>9.743237733840942</v>
+        <v>61.92353343963623</v>
       </c>
       <c r="K9" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="P9" t="n">
-        <v>1.303999057811133</v>
+        <v>3.082908084335546</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.277113281921585</v>
+        <v>63.68552276024423</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3562860180787232</v>
+        <v>0.1913050385621362</v>
       </c>
       <c r="S9" t="n">
-        <v>5.937398357811441</v>
+        <v>66.9597358831419</v>
       </c>
       <c r="T9" t="n">
-        <v>168.4239358277799</v>
+        <v>14.9343480348429</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8.069807767868042</v>
+        <v>64.00447082519531</v>
       </c>
       <c r="K10" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="P10" t="n">
-        <v>1.167614981910359</v>
+        <v>3.420832001205759</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.40827184698421</v>
+        <v>66.0140007686731</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3071769952105361</v>
+        <v>0.201378977107449</v>
       </c>
       <c r="S10" t="n">
-        <v>4.883063824105106</v>
+        <v>69.63621174698631</v>
       </c>
       <c r="T10" t="n">
-        <v>204.7894592455516</v>
+        <v>14.36034463840974</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1470,37 +1470,37 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>9.740017175674438</v>
+        <v>63.34791970252991</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="N11" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="O11" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="P11" t="n">
-        <v>1.246810051796559</v>
+        <v>3.114497473501593</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.223361703643824</v>
+        <v>64.71123215180988</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3660892397540492</v>
+        <v>0.1901969301299511</v>
       </c>
       <c r="S11" t="n">
-        <v>5.836260995194432</v>
+        <v>68.01592655544142</v>
       </c>
       <c r="T11" t="n">
-        <v>171.3425771779909</v>
+        <v>14.70243883518775</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1567,37 +1567,37 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>9.596434593200684</v>
+        <v>58.4327507019043</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="N12" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="O12" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="P12" t="n">
-        <v>1.260260268671951</v>
+        <v>3.072257202399329</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.050318887940708</v>
+        <v>60.14954761686918</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3390045204611512</v>
+        <v>0.1889928795246459</v>
       </c>
       <c r="S12" t="n">
-        <v>5.649583677073811</v>
+        <v>63.41079769879315</v>
       </c>
       <c r="T12" t="n">
-        <v>177.0041930802851</v>
+        <v>15.77018483114008</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1664,37 +1664,37 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>9.07709002494812</v>
+        <v>58.60601186752319</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="N13" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="O13" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="P13" t="n">
-        <v>1.215600822889614</v>
+        <v>3.035289937345197</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.836754749436405</v>
+        <v>60.19008606988199</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3256693349744254</v>
+        <v>0.1863357096445692</v>
       </c>
       <c r="S13" t="n">
-        <v>5.378024907300444</v>
+        <v>63.41171171687176</v>
       </c>
       <c r="T13" t="n">
-        <v>185.941868480851</v>
+        <v>15.76995751928162</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1761,37 +1761,37 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10.14369201660156</v>
+        <v>59.18736863136292</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9183375572963551</v>
+        <v>0.9190307552534429</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="P14" t="n">
-        <v>1.267715632577647</v>
+        <v>2.939649191577416</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.43443337350022</v>
+        <v>59.31122958553966</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3671151903871354</v>
+        <v>0.1898501807219478</v>
       </c>
       <c r="S14" t="n">
-        <v>6.069264196465003</v>
+        <v>62.44072895783903</v>
       </c>
       <c r="T14" t="n">
-        <v>164.7646185154442</v>
+        <v>16.01518778993141</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1858,37 +1858,37 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>8.955272197723389</v>
+        <v>58.07856726646423</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9183375572963551</v>
+        <v>0.9190307552534429</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="P15" t="n">
-        <v>1.194461401231031</v>
+        <v>3.254788601205576</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.783325237326422</v>
+        <v>59.18442078434263</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3344970337700461</v>
+        <v>0.1847110012005876</v>
       </c>
       <c r="S15" t="n">
-        <v>5.312283672327498</v>
+        <v>62.62392038674879</v>
       </c>
       <c r="T15" t="n">
-        <v>188.2429594656538</v>
+        <v>15.96833915577728</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1955,37 +1955,37 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>9.618680715560913</v>
+        <v>58.37568521499634</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9183375572963551</v>
+        <v>0.9190307552534429</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="P16" t="n">
-        <v>1.239635516876332</v>
+        <v>3.179339691577439</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.153844390382429</v>
+        <v>59.45247530481505</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3299652867877213</v>
+        <v>0.1850417975926674</v>
       </c>
       <c r="S16" t="n">
-        <v>5.723445194046482</v>
+        <v>62.81685679398516</v>
       </c>
       <c r="T16" t="n">
-        <v>174.7199398432605</v>
+        <v>15.91929381757529</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2052,37 +2052,37 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10.05600571632385</v>
+        <v>58.54555773735046</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="P17" t="n">
-        <v>1.312469904804451</v>
+        <v>2.257072510839687</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.492682968621779</v>
+        <v>59.76109326506629</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3570374590423623</v>
+        <v>0.1917534168728433</v>
       </c>
       <c r="S17" t="n">
-        <v>6.162190332468593</v>
+        <v>62.20991919277882</v>
       </c>
       <c r="T17" t="n">
-        <v>162.2799598920205</v>
+        <v>16.07460695940074</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2149,37 +2149,37 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8.084418058395386</v>
+        <v>60.11703562736511</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="P18" t="n">
-        <v>1.174304463906499</v>
+        <v>3.185337322891274</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.402678697609398</v>
+        <v>61.61327758193101</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3022753277540884</v>
+        <v>0.1924727746920479</v>
       </c>
       <c r="S18" t="n">
-        <v>4.879258489269986</v>
+        <v>64.99108767951434</v>
       </c>
       <c r="T18" t="n">
-        <v>204.9491745926369</v>
+        <v>15.38672509885086</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2246,37 +2246,37 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>9.823601245880127</v>
+        <v>59.21114325523376</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="P19" t="n">
-        <v>1.272385986694973</v>
+        <v>3.215766483129531</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.331263360222966</v>
+        <v>61.09331517349489</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3429453711004202</v>
+        <v>0.1928231807224039</v>
       </c>
       <c r="S19" t="n">
-        <v>5.946594718018359</v>
+        <v>64.50190483734681</v>
       </c>
       <c r="T19" t="n">
-        <v>168.1634695853696</v>
+        <v>15.50341811643672</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2343,37 +2343,37 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>9.939846038818359</v>
+        <v>59.42232847213745</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="P20" t="n">
-        <v>1.287515624090998</v>
+        <v>3.03285987229119</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.268527997595241</v>
+        <v>60.37858796024515</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3333776963875399</v>
+        <v>0.1890228277206697</v>
       </c>
       <c r="S20" t="n">
-        <v>5.889421318073778</v>
+        <v>63.60047066025701</v>
       </c>
       <c r="T20" t="n">
-        <v>169.7959690761375</v>
+        <v>15.72315408390343</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2440,37 +2440,37 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8.348035335540771</v>
+        <v>56.87005281448364</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="P21" t="n">
-        <v>1.159636200062811</v>
+        <v>1.717446163850702</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.487645795207919</v>
+        <v>60.31156338191199</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3064756710736252</v>
+        <v>0.1693475192803225</v>
       </c>
       <c r="S21" t="n">
-        <v>4.953757666344354</v>
+        <v>62.19835706504301</v>
       </c>
       <c r="T21" t="n">
-        <v>201.8669598624016</v>
+        <v>16.07759508750793</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2537,37 +2537,37 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>10.04682850837708</v>
+        <v>58.58240652084351</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="O22" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="P22" t="n">
-        <v>1.322087873500479</v>
+        <v>1.761506943363333</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.354311033686432</v>
+        <v>62.04982790481406</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3521451650925314</v>
+        <v>0.1764253036099145</v>
       </c>
       <c r="S22" t="n">
-        <v>6.028544072279443</v>
+        <v>63.98776015178731</v>
       </c>
       <c r="T22" t="n">
-        <v>165.8775299658532</v>
+        <v>15.62798881579648</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2634,37 +2634,37 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>9.089143037796021</v>
+        <v>61.29265928268433</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983445</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="O23" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="P23" t="n">
-        <v>1.213023071072548</v>
+        <v>3.185828581927783</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.805790138599205</v>
+        <v>62.11044081686062</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3160019493724938</v>
+        <v>0.1901159879444861</v>
       </c>
       <c r="S23" t="n">
-        <v>5.334815159044246</v>
+        <v>65.48638538673288</v>
       </c>
       <c r="T23" t="n">
-        <v>187.4479190351469</v>
+        <v>15.2703496168624</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2731,37 +2731,37 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>9.113104343414307</v>
+        <v>59.56893801689148</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983445</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="P24" t="n">
-        <v>1.234613444598452</v>
+        <v>3.347849456626334</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.879838393970795</v>
+        <v>61.25626890120493</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3185821192970931</v>
+        <v>0.1960719313287937</v>
       </c>
       <c r="S24" t="n">
-        <v>5.43303395786634</v>
+        <v>64.80019028916004</v>
       </c>
       <c r="T24" t="n">
-        <v>184.0592213770591</v>
+        <v>15.43205344826407</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2828,37 +2828,37 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>9.975719928741455</v>
+        <v>58.88414597511292</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983445</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="O25" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="P25" t="n">
-        <v>1.331740408425843</v>
+        <v>3.251770795190256</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.357297768676443</v>
+        <v>60.6550611361443</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3365261108437076</v>
+        <v>0.1936560132555796</v>
       </c>
       <c r="S25" t="n">
-        <v>6.025564287945993</v>
+        <v>64.10048794459013</v>
       </c>
       <c r="T25" t="n">
-        <v>165.959560335366</v>
+        <v>15.60050527016927</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2925,37 +2925,37 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>8.155663728713989</v>
+        <v>60.26346230506897</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="M26" t="n">
-        <v>0.9083748763111517</v>
+        <v>0.9345543815455291</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="P26" t="n">
-        <v>1.180629424121128</v>
+        <v>2.97798864938334</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.429347692751862</v>
+        <v>61.4793184903581</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3083778614886084</v>
+        <v>0.1960975228950745</v>
       </c>
       <c r="S26" t="n">
-        <v>4.918354978361599</v>
+        <v>64.6534046626365</v>
       </c>
       <c r="T26" t="n">
-        <v>203.3200133783592</v>
+        <v>15.46708955573231</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3022,37 +3022,37 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>9.99750018119812</v>
+        <v>58.92950129508972</v>
       </c>
       <c r="K27" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9083748763111517</v>
+        <v>0.9345543815455291</v>
       </c>
       <c r="N27" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="O27" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="P27" t="n">
-        <v>1.372347184316099</v>
+        <v>3.161754009643557</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.394243479531812</v>
+        <v>60.90852873614045</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3416154060643573</v>
+        <v>0.1978242156585922</v>
       </c>
       <c r="S27" t="n">
-        <v>6.108206069912269</v>
+        <v>64.26810696144261</v>
       </c>
       <c r="T27" t="n">
-        <v>163.7141885120393</v>
+        <v>15.55981726052622</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3119,37 +3119,37 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>10.2380223274231</v>
+        <v>59.08849263191223</v>
       </c>
       <c r="K28" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="L28" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9083748763111517</v>
+        <v>0.9345543815455291</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="O28" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="P28" t="n">
-        <v>1.289885173462674</v>
+        <v>3.331985312055928</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.420830131331683</v>
+        <v>60.94101171445811</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3510638469576286</v>
+        <v>0.194970909639329</v>
       </c>
       <c r="S28" t="n">
-        <v>6.061779151751985</v>
+        <v>64.46796793615336</v>
       </c>
       <c r="T28" t="n">
-        <v>164.9680687741615</v>
+        <v>15.51157934728705</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3216,37 +3216,37 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>8.191219329833984</v>
+        <v>59.98239517211914</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230805</v>
       </c>
       <c r="L29" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="M29" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="P29" t="n">
-        <v>1.168852561401643</v>
+        <v>3.083654514463328</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.465931490374868</v>
+        <v>61.13945347229586</v>
       </c>
       <c r="R29" t="n">
-        <v>0.3117338686999837</v>
+        <v>0.1972950204831195</v>
       </c>
       <c r="S29" t="n">
-        <v>4.946517920476494</v>
+        <v>64.42040300724231</v>
       </c>
       <c r="T29" t="n">
-        <v>202.1624132524462</v>
+        <v>15.5230323518401</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3313,37 +3313,37 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>9.817988395690918</v>
+        <v>58.35378503799438</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230805</v>
       </c>
       <c r="L30" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="M30" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="N30" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="P30" t="n">
-        <v>1.258959024065018</v>
+        <v>2.205893674699179</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.402442960211824</v>
+        <v>61.41809269757654</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3507585229217292</v>
+        <v>0.1966948734941278</v>
       </c>
       <c r="S30" t="n">
-        <v>6.01216050719857</v>
+        <v>63.82068124576985</v>
       </c>
       <c r="T30" t="n">
-        <v>166.3295580353627</v>
+        <v>15.66890199979308</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3410,37 +3410,37 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>8.79565954208374</v>
+        <v>59.64615654945374</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230805</v>
       </c>
       <c r="L31" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="M31" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="N31" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="O31" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="P31" t="n">
-        <v>1.217432613242614</v>
+        <v>3.180622025290056</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.726073743380394</v>
+        <v>61.74032578312481</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3182634494060697</v>
+        <v>0.199364475915297</v>
       </c>
       <c r="S31" t="n">
-        <v>5.261769806029077</v>
+        <v>65.12031228433017</v>
       </c>
       <c r="T31" t="n">
-        <v>190.0501232216911</v>
+        <v>15.35619171532488</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3507,37 +3507,37 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>9.296525001525879</v>
+        <v>60.03535008430481</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="L32" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="M32" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585607</v>
       </c>
       <c r="N32" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="O32" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="P32" t="n">
-        <v>1.254318056626618</v>
+        <v>3.022330383129818</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.983685985532433</v>
+        <v>60.83191081083842</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3192824216616335</v>
+        <v>0.196049425290131</v>
       </c>
       <c r="S32" t="n">
-        <v>5.557286463820684</v>
+        <v>64.05029061925836</v>
       </c>
       <c r="T32" t="n">
-        <v>179.9439360396928</v>
+        <v>15.61273165713513</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3604,37 +3604,37 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>10.09921073913574</v>
+        <v>58.71746230125427</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="L33" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="M33" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585607</v>
       </c>
       <c r="N33" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="O33" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="P33" t="n">
-        <v>1.348155501199723</v>
+        <v>3.174449668675327</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.368008666259187</v>
+        <v>60.52263838673807</v>
       </c>
       <c r="R33" t="n">
-        <v>0.343429538593063</v>
+        <v>0.1940091337358803</v>
       </c>
       <c r="S33" t="n">
-        <v>6.059593706051974</v>
+        <v>63.89109718914928</v>
       </c>
       <c r="T33" t="n">
-        <v>165.0275659573112</v>
+        <v>15.65163291905138</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3701,37 +3701,37 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>8.495866537094116</v>
+        <v>59.45911145210266</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="L34" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="M34" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585607</v>
       </c>
       <c r="N34" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="O34" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="P34" t="n">
-        <v>1.191541687975072</v>
+        <v>3.193636939760332</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.659971907216525</v>
+        <v>61.35913351927667</v>
       </c>
       <c r="R34" t="n">
-        <v>0.3118361048262772</v>
+        <v>0.1982441289060097</v>
       </c>
       <c r="S34" t="n">
-        <v>5.163349700017873</v>
+        <v>64.75101458794302</v>
       </c>
       <c r="T34" t="n">
-        <v>193.6727237352408</v>
+        <v>15.44377345071293</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3798,37 +3798,37 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>10.23582220077515</v>
+        <v>59.85925340652466</v>
       </c>
       <c r="K35" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="L35" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="M35" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818113</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="P35" t="n">
-        <v>1.354511483099574</v>
+        <v>2.748429346989855</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.551339444554627</v>
+        <v>61.05294079395635</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3435342987512444</v>
+        <v>0.1962123385603636</v>
       </c>
       <c r="S35" t="n">
-        <v>6.249385226405446</v>
+        <v>63.99758247950657</v>
       </c>
       <c r="T35" t="n">
-        <v>160.015739752242</v>
+        <v>15.6255902372597</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3895,37 +3895,37 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9.884141206741333</v>
+        <v>58.94184541702271</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="L36" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="M36" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818113</v>
       </c>
       <c r="N36" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="P36" t="n">
-        <v>1.320186569895427</v>
+        <v>3.185024238555672</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.238427045819695</v>
+        <v>60.79805563854937</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3313429987681146</v>
+        <v>0.1937291132495616</v>
       </c>
       <c r="S36" t="n">
-        <v>5.889956614483237</v>
+        <v>64.1768089903546</v>
       </c>
       <c r="T36" t="n">
-        <v>169.7805375239994</v>
+        <v>15.58195266689396</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3992,37 +3992,37 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>8.618870258331299</v>
+        <v>59.05126905441284</v>
       </c>
       <c r="K37" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="L37" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="M37" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818113</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="P37" t="n">
-        <v>1.200417616807926</v>
+        <v>2.223207268669131</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.633441634975684</v>
+        <v>62.01846860723605</v>
       </c>
       <c r="R37" t="n">
-        <v>0.3113038506020837</v>
+        <v>0.1960108638565752</v>
       </c>
       <c r="S37" t="n">
-        <v>5.145163102385694</v>
+        <v>64.43768673976176</v>
       </c>
       <c r="T37" t="n">
-        <v>194.3572983208876</v>
+        <v>15.51886870238845</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4089,37 +4089,37 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10.06005048751831</v>
+        <v>60.76770091056824</v>
       </c>
       <c r="K38" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.9235417287411419</v>
       </c>
       <c r="N38" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="O38" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="P38" t="n">
-        <v>1.323305284309009</v>
+        <v>2.955306515659357</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.536971578292365</v>
+        <v>61.96392989034953</v>
       </c>
       <c r="R38" t="n">
-        <v>0.329991133737375</v>
+        <v>0.1966932481892915</v>
       </c>
       <c r="S38" t="n">
-        <v>6.190267996338749</v>
+        <v>65.11592965419817</v>
       </c>
       <c r="T38" t="n">
-        <v>161.5438944794398</v>
+        <v>15.3572252643947</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4186,37 +4186,37 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>9.060518503189087</v>
+        <v>60.72129988670349</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="M39" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.9235417287411419</v>
       </c>
       <c r="N39" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="O39" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="P39" t="n">
-        <v>1.242350834976364</v>
+        <v>3.087567839757176</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.878452881949067</v>
+        <v>62.31374739637946</v>
       </c>
       <c r="R39" t="n">
-        <v>0.3196563265378081</v>
+        <v>0.1975734156624103</v>
       </c>
       <c r="S39" t="n">
-        <v>5.44046004346324</v>
+        <v>65.59888865179904</v>
       </c>
       <c r="T39" t="n">
-        <v>183.8079853562216</v>
+        <v>15.24416069467322</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4283,37 +4283,37 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>9.675210237503052</v>
+        <v>60.51085138320923</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L40" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="M40" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.9235417287411419</v>
       </c>
       <c r="N40" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="P40" t="n">
-        <v>1.253963098839362</v>
+        <v>3.210709798797478</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.264567971090783</v>
+        <v>61.95215227952736</v>
       </c>
       <c r="R40" t="n">
-        <v>0.3213423530274689</v>
+        <v>0.1968657578323385</v>
       </c>
       <c r="S40" t="n">
-        <v>5.839873422957614</v>
+        <v>65.35972783615718</v>
       </c>
       <c r="T40" t="n">
-        <v>171.2365881200124</v>
+        <v>15.29994131105909</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4380,37 +4380,37 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>10.18562650680542</v>
+        <v>61.24172377586365</v>
       </c>
       <c r="K41" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="L41" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="M41" t="n">
-        <v>0.9021413829153113</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="N41" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="O41" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="P41" t="n">
-        <v>1.353970868677355</v>
+        <v>3.05711818673773</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.540262954215434</v>
+        <v>61.99581863132657</v>
       </c>
       <c r="R41" t="n">
-        <v>0.3652344819740217</v>
+        <v>0.1947455072317405</v>
       </c>
       <c r="S41" t="n">
-        <v>6.25946830486681</v>
+        <v>65.24768232529604</v>
       </c>
       <c r="T41" t="n">
-        <v>159.7579780414398</v>
+        <v>15.32621488399301</v>
       </c>
       <c r="U41" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4477,37 +4477,37 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>8.409804105758667</v>
+        <v>60.31957316398621</v>
       </c>
       <c r="K42" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9021413829153113</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="N42" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="P42" t="n">
-        <v>1.198618190381196</v>
+        <v>3.180057955422996</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.54956285903109</v>
+        <v>62.49200188795807</v>
       </c>
       <c r="R42" t="n">
-        <v>0.3139827542239449</v>
+        <v>0.2000162108425322</v>
       </c>
       <c r="S42" t="n">
-        <v>5.06216380363623</v>
+        <v>65.8720760542236</v>
       </c>
       <c r="T42" t="n">
-        <v>197.5439829271594</v>
+        <v>15.18093947998291</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4574,37 +4574,37 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>10.1173894405365</v>
+        <v>61.44903373718262</v>
       </c>
       <c r="K43" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="L43" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="M43" t="n">
-        <v>0.9021413829153113</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="N43" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="P43" t="n">
-        <v>1.325706149408831</v>
+        <v>3.391078795179252</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.455786550575597</v>
+        <v>63.57149296024206</v>
       </c>
       <c r="R43" t="n">
-        <v>0.3435886433169755</v>
+        <v>0.203368862641407</v>
       </c>
       <c r="S43" t="n">
-        <v>6.125081343301403</v>
+        <v>67.16594061806272</v>
       </c>
       <c r="T43" t="n">
-        <v>163.2631378999781</v>
+        <v>14.88849840853823</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4671,37 +4671,37 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>10.02762985229492</v>
+        <v>60.53310775756836</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="M44" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="O44" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="P44" t="n">
-        <v>1.276974920521358</v>
+        <v>2.811398706029628</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.449955990339621</v>
+        <v>62.38498326022976</v>
       </c>
       <c r="R44" t="n">
-        <v>0.3397417710698665</v>
+        <v>0.1978427023930701</v>
       </c>
       <c r="S44" t="n">
-        <v>6.066672681930846</v>
+        <v>65.39422466865246</v>
       </c>
       <c r="T44" t="n">
-        <v>164.8350013968001</v>
+        <v>15.29187026938424</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4768,37 +4768,37 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>8.502555131912231</v>
+        <v>59.51439237594604</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="L45" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="M45" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="N45" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="P45" t="n">
-        <v>1.205356446954251</v>
+        <v>3.16815523733512</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.696078893947096</v>
+        <v>61.75980855540762</v>
       </c>
       <c r="R45" t="n">
-        <v>0.3279016348982163</v>
+        <v>0.1943270421694492</v>
       </c>
       <c r="S45" t="n">
-        <v>5.229336975799563</v>
+        <v>65.12229083491218</v>
       </c>
       <c r="T45" t="n">
-        <v>191.2288316143751</v>
+        <v>15.35572516229571</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4865,37 +4865,37 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>10.00291419029236</v>
+        <v>59.64236378669739</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="L46" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="N46" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="O46" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="P46" t="n">
-        <v>1.25702875898625</v>
+        <v>3.258446079503465</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.532991957815953</v>
+        <v>61.78047201445619</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3341426999531357</v>
+        <v>0.1950430289268177</v>
       </c>
       <c r="S46" t="n">
-        <v>6.124163416755338</v>
+        <v>65.23396112288647</v>
       </c>
       <c r="T46" t="n">
-        <v>163.2876087636821</v>
+        <v>15.32943857442934</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4962,37 +4962,37 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>9.153937816619873</v>
+        <v>60.10424399375916</v>
       </c>
       <c r="K47" t="n">
-        <v>0.4352710502413851</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L47" t="n">
-        <v>0.1221242193075461</v>
+        <v>0.2174558723178379</v>
       </c>
       <c r="M47" t="n">
-        <v>0.1271027450111713</v>
+        <v>0.2184629615009359</v>
       </c>
       <c r="N47" t="n">
-        <v>0.07292086991843218</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="O47" t="n">
-        <v>0.07292086991843218</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="P47" t="n">
-        <v>1.249511292757321</v>
+        <v>2.674301946975113</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.033442353003526</v>
+        <v>62.22300034939497</v>
       </c>
       <c r="R47" t="n">
-        <v>0.3289966337707669</v>
+        <v>0.1964590529945759</v>
       </c>
       <c r="S47" t="n">
-        <v>5.611950279531614</v>
+        <v>65.09376134936466</v>
       </c>
       <c r="T47" t="n">
-        <v>178.191172442722</v>
+        <v>15.36245531477127</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5059,37 +5059,37 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>9.04016900062561</v>
+        <v>59.84819507598877</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4352710502413851</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L48" t="n">
-        <v>0.1221242193075461</v>
+        <v>0.2174558723178379</v>
       </c>
       <c r="M48" t="n">
-        <v>0.1271027450111713</v>
+        <v>0.2184629615009359</v>
       </c>
       <c r="N48" t="n">
-        <v>0.07292086991843218</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="O48" t="n">
-        <v>0.07292086991843218</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="P48" t="n">
-        <v>1.225113700016357</v>
+        <v>2.942382880705572</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.98111584937254</v>
+        <v>62.62514821565203</v>
       </c>
       <c r="R48" t="n">
-        <v>0.3234090602427934</v>
+        <v>0.1982536879643386</v>
       </c>
       <c r="S48" t="n">
-        <v>5.52963860963169</v>
+        <v>65.76578478432194</v>
       </c>
       <c r="T48" t="n">
-        <v>180.8436446928322</v>
+        <v>15.20547505484025</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5156,37 +5156,37 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>9.965587139129639</v>
+        <v>59.67401480674744</v>
       </c>
       <c r="K49" t="n">
-        <v>0.4352710502413851</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L49" t="n">
-        <v>0.1221242193075461</v>
+        <v>0.2174558723178379</v>
       </c>
       <c r="M49" t="n">
-        <v>0.1271027450111713</v>
+        <v>0.2184629615009359</v>
       </c>
       <c r="N49" t="n">
-        <v>0.07292086991843218</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="O49" t="n">
-        <v>0.07292086991843218</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="P49" t="n">
-        <v>1.319577486719936</v>
+        <v>3.002698403597825</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.397309184305304</v>
+        <v>62.33669640362469</v>
       </c>
       <c r="R49" t="n">
-        <v>0.3338473891514684</v>
+        <v>0.1961259855525863</v>
       </c>
       <c r="S49" t="n">
-        <v>6.050734060176709</v>
+        <v>65.5355207927751</v>
       </c>
       <c r="T49" t="n">
-        <v>165.269203712251</v>
+        <v>15.25890063744247</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -5393,73 +5393,73 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9021413829153113</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.292765069489127</v>
+        <v>3.20941831244666</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08274931856610483</v>
+        <v>0.1689051358635247</v>
       </c>
       <c r="P2" t="n">
-        <v>4.181870787940707</v>
+        <v>62.6864378265089</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5492213155135708</v>
+        <v>0.8056310559747104</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3409352931716474</v>
+        <v>0.1993768602385599</v>
       </c>
       <c r="S2" t="n">
-        <v>0.02572868243006785</v>
+        <v>0.00434708425573466</v>
       </c>
       <c r="T2" t="n">
-        <v>5.815571150601481</v>
+        <v>66.09523299919412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6559206786690056</v>
+        <v>0.9784058391120121</v>
       </c>
       <c r="V2" t="n">
-        <v>173.5216996228591</v>
+        <v>15.13188425750472</v>
       </c>
       <c r="W2" t="n">
-        <v>20.87759822806558</v>
+        <v>0.2229433546002845</v>
       </c>
       <c r="X2" t="n">
-        <v>9.570940017700195</v>
+        <v>61.00344355901083</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.006151841822824</v>
+        <v>0.6012515221676051</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.560777518437154</v>
+        <v>0.7176594867116615</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.79584127122101</v>
+        <v>3.312618312228618</v>
       </c>
       <c r="AB2" t="n">
-        <v>-9.381426778907139</v>
+        <v>0.504344114684448</v>
       </c>
     </row>
     <row r="3">
@@ -5487,73 +5487,73 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7205195768217173</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.246453375487286</v>
+        <v>3.079333340956071</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03696187889073316</v>
+        <v>0.2363891611088422</v>
       </c>
       <c r="P3" t="n">
-        <v>4.22634228070089</v>
+        <v>61.97508794336452</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4610945537223199</v>
+        <v>0.3551300785993827</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3339287019737395</v>
+        <v>0.1957375911631123</v>
       </c>
       <c r="S3" t="n">
-        <v>0.005922968216375502</v>
+        <v>0.001857896452187931</v>
       </c>
       <c r="T3" t="n">
-        <v>5.806724358161915</v>
+        <v>65.25015887548371</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5008577024775623</v>
+        <v>0.1366886164794673</v>
       </c>
       <c r="V3" t="n">
-        <v>173.1171472582857</v>
+        <v>15.32567800203643</v>
       </c>
       <c r="W3" t="n">
-        <v>15.70424906358834</v>
+        <v>0.0320931186662423</v>
       </c>
       <c r="X3" t="n">
-        <v>9.511033058166504</v>
+        <v>59.89662130673727</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8734549283126432</v>
+        <v>0.5549147881081347</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.97621072776555</v>
+        <v>19.86799777064885</v>
       </c>
       <c r="AA3" t="n">
-        <v>31.90496106468513</v>
+        <v>27.96394748528498</v>
       </c>
       <c r="AB3" t="n">
-        <v>-9.592696943679231</v>
+        <v>1.791501276095386</v>
       </c>
     </row>
     <row r="4">
@@ -5581,73 +5581,73 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.4352710502413851</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1221242193075461</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1271027450111713</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07292086991843218</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1.264734159831205</v>
+        <v>2.873127743759503</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04903726655368016</v>
+        <v>0.1748092207969942</v>
       </c>
       <c r="P4" t="n">
-        <v>4.13728912889379</v>
+        <v>62.39494832289057</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2266987817737805</v>
+        <v>0.2073057914227061</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3287510277216762</v>
+        <v>0.1969462421705002</v>
       </c>
       <c r="S4" t="n">
-        <v>0.005223496850763162</v>
+        <v>0.001144462475617925</v>
       </c>
       <c r="T4" t="n">
-        <v>5.730774316446671</v>
+        <v>65.46502230882056</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2801329701343132</v>
+        <v>0.3415133986578889</v>
       </c>
       <c r="V4" t="n">
-        <v>174.7680069492684</v>
+        <v>15.27561033568467</v>
       </c>
       <c r="W4" t="n">
-        <v>8.332427585108718</v>
+        <v>0.07981297522027193</v>
       </c>
       <c r="X4" t="n">
-        <v>9.38656465212504</v>
+        <v>59.87548462549845</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5046643599620709</v>
+        <v>0.2164089369077023</v>
       </c>
       <c r="Z4" t="n">
-        <v>86.4126730728853</v>
+        <v>76.69773960516709</v>
       </c>
       <c r="AA4" t="n">
-        <v>90.93202006388171</v>
+        <v>84.29634297168511</v>
       </c>
       <c r="AB4" t="n">
-        <v>-8.730565290345913</v>
+        <v>1.458957233172154</v>
       </c>
     </row>
     <row r="5">
@@ -5675,73 +5675,73 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9183375572963551</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781358</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.233937516895003</v>
+        <v>3.12459249478681</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03695803032341279</v>
+        <v>0.1645483319347854</v>
       </c>
       <c r="P5" t="n">
-        <v>4.12386766706969</v>
+        <v>59.31604189156578</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3265875138509676</v>
+        <v>0.1340920400448596</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3438591703149676</v>
+        <v>0.1865343265050676</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02026736378702856</v>
+        <v>0.002876373316166564</v>
       </c>
       <c r="T5" t="n">
-        <v>5.701664354279661</v>
+        <v>62.62716871285766</v>
       </c>
       <c r="U5" t="n">
-        <v>0.378960000813521</v>
+        <v>0.1880849568622517</v>
       </c>
       <c r="V5" t="n">
-        <v>175.9091726081195</v>
+        <v>15.96760692109466</v>
       </c>
       <c r="W5" t="n">
-        <v>11.78426193574861</v>
+        <v>0.04795117943577574</v>
       </c>
       <c r="X5" t="n">
-        <v>9.572548309961954</v>
+        <v>58.54720703760783</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5955514802352253</v>
+        <v>0.5739555021291026</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.829400935937223</v>
+        <v>1.97196896608061</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.154746520458132</v>
+        <v>1.798220248652718</v>
       </c>
       <c r="AB5" t="n">
-        <v>-8.134612138441828</v>
+        <v>6.055123960507485</v>
       </c>
     </row>
     <row r="6">
@@ -5769,73 +5769,73 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.885160432857265</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7480057530889145</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.253053451801974</v>
+        <v>2.88605877228683</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07108257482444727</v>
+        <v>0.5449305196675466</v>
       </c>
       <c r="P6" t="n">
-        <v>4.075541675484714</v>
+        <v>60.82256200683073</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5882792812434716</v>
+        <v>0.9553152065438445</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3340860526322904</v>
+        <v>0.1923497907624317</v>
       </c>
       <c r="S6" t="n">
-        <v>0.02843568881877748</v>
+        <v>0.000545382855125205</v>
       </c>
       <c r="T6" t="n">
-        <v>5.662681179918979</v>
+        <v>63.90097056987999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.686974309134137</v>
+        <v>1.48477810910068</v>
       </c>
       <c r="V6" t="n">
-        <v>178.4642013566757</v>
+        <v>15.65491672489611</v>
       </c>
       <c r="W6" t="n">
-        <v>23.12453841831485</v>
+        <v>0.3681157899251804</v>
       </c>
       <c r="X6" t="n">
-        <v>9.321341673533121</v>
+        <v>59.29124553998312</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.077491522813341</v>
+        <v>0.7887952660340783</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.823107294368561</v>
+        <v>3.926616133732436</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.982717448399336</v>
+        <v>4.632303340050877</v>
       </c>
       <c r="AB6" t="n">
-        <v>-6.800294527236643</v>
+        <v>3.97826938342854</v>
       </c>
     </row>
     <row r="7">
@@ -5863,73 +5863,73 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459415</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.256413232551429</v>
+        <v>2.170604326501742</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08557543818342483</v>
+        <v>0.747060109868215</v>
       </c>
       <c r="P7" t="n">
-        <v>4.036828275496531</v>
+        <v>60.91332641565706</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.477536103150557</v>
+        <v>0.984809524561593</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3306661775178988</v>
+        <v>0.1782652168703022</v>
       </c>
       <c r="S7" t="n">
-        <v>0.02295517200809092</v>
+        <v>0.009965861787121676</v>
       </c>
       <c r="T7" t="n">
-        <v>5.623907685565858</v>
+        <v>63.26219595902911</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5845208049174806</v>
+        <v>0.9414420756640458</v>
       </c>
       <c r="V7" t="n">
-        <v>179.1801529681308</v>
+        <v>15.80957932906928</v>
       </c>
       <c r="W7" t="n">
-        <v>19.74479542964939</v>
+        <v>0.2369355231746632</v>
       </c>
       <c r="X7" t="n">
-        <v>9.444903294245401</v>
+        <v>58.29159593582153</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.9514204125006295</v>
+        <v>1.300752034568335</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.170931904528223</v>
+        <v>5.791645736798458</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.866175606361049</v>
+        <v>8.951380806422364</v>
       </c>
       <c r="AB7" t="n">
-        <v>-6.426401730736791</v>
+        <v>5.005521728673294</v>
       </c>
     </row>
     <row r="8">
@@ -5957,73 +5957,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9344103520410755</v>
+        <v>0.9362675415983445</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7952145538510432</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.259792308032281</v>
+        <v>3.261816277914791</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06323711663199527</v>
+        <v>0.08147622200309464</v>
       </c>
       <c r="P8" t="n">
-        <v>4.014308767082148</v>
+        <v>61.34059028473661</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2993357269720453</v>
+        <v>0.7313447036459689</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3237033931710981</v>
+        <v>0.1932813108429532</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01117948503257368</v>
+        <v>0.00299559957651059</v>
       </c>
       <c r="T8" t="n">
-        <v>5.597804468285527</v>
+        <v>64.79568787349434</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3736918257033194</v>
+        <v>0.6929596913562658</v>
       </c>
       <c r="V8" t="n">
-        <v>179.1555669158573</v>
+        <v>15.43430277843191</v>
       </c>
       <c r="W8" t="n">
-        <v>11.55299788837336</v>
+        <v>0.1650893196644596</v>
       </c>
       <c r="X8" t="n">
-        <v>9.392655769983927</v>
+        <v>59.91524775822958</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5050904829458293</v>
+        <v>1.241040658438067</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.1112136787719119</v>
+        <v>0.1334143615863452</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.112128430494858</v>
+        <v>0.2546603051363033</v>
       </c>
       <c r="AB8" t="n">
-        <v>-6.43924135242676</v>
+        <v>2.512975331834195</v>
       </c>
     </row>
     <row r="9">
@@ -6051,73 +6051,73 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.280953927299967</v>
+        <v>3.157242657027608</v>
       </c>
       <c r="O9" t="n">
-        <v>0.09617042301070687</v>
+        <v>0.1770414457765514</v>
       </c>
       <c r="P9" t="n">
-        <v>4.081473767871786</v>
+        <v>61.10961964698555</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5649141756957149</v>
+        <v>0.3205802739772734</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3336857048368647</v>
+        <v>0.1962975493976652</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02242060347165801</v>
+        <v>0.001437131434905976</v>
       </c>
       <c r="T9" t="n">
-        <v>5.696113400008618</v>
+        <v>64.46315985341083</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6739584456883166</v>
+        <v>0.1926938449485868</v>
       </c>
       <c r="V9" t="n">
-        <v>177.33409022152</v>
+        <v>15.51282872118186</v>
       </c>
       <c r="W9" t="n">
-        <v>22.51320069787498</v>
+        <v>0.04637647583024324</v>
       </c>
       <c r="X9" t="n">
-        <v>9.463728745778402</v>
+        <v>59.42715207735697</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.139183168922785</v>
+        <v>0.7286155769868764</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.89441494176859</v>
+        <v>0.3161478619218554</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.253651765545279</v>
+        <v>0.5395366570970905</v>
       </c>
       <c r="AB9" t="n">
-        <v>-7.390474653824032</v>
+        <v>3.034536178967733</v>
       </c>
     </row>
     <row r="10">
@@ -6145,73 +6145,73 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8423088650259937</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.215081399569758</v>
+        <v>2.823390071484188</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04509922180845374</v>
+        <v>0.5369609153102622</v>
       </c>
       <c r="P10" t="n">
-        <v>3.864816064655695</v>
+        <v>61.4326239843324</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4834258030646357</v>
+        <v>0.3006996045912227</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3269186136759275</v>
+        <v>0.1977847899641814</v>
       </c>
       <c r="S10" t="n">
-        <v>0.02090250728227043</v>
+        <v>0.001400571269237239</v>
       </c>
       <c r="T10" t="n">
-        <v>5.40681607790138</v>
+        <v>64.45379884578078</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5474279371725285</v>
+        <v>0.6504588154688254</v>
       </c>
       <c r="V10" t="n">
-        <v>186.1806981698334</v>
+        <v>15.51604202231936</v>
       </c>
       <c r="W10" t="n">
-        <v>18.22711485469044</v>
+        <v>0.1564722947781884</v>
       </c>
       <c r="X10" t="n">
-        <v>8.934955755869547</v>
+        <v>59.32744558652242</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.8222815666111919</v>
+        <v>0.8598111715155357</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.564388177626981</v>
+        <v>1.526643018680312</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.614860405212791</v>
+        <v>4.183858364223433</v>
       </c>
       <c r="AB10" t="n">
-        <v>-2.770493453404039</v>
+        <v>3.055878578748954</v>
       </c>
     </row>
     <row r="11">
@@ -6239,73 +6239,73 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585607</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.264671748600471</v>
+        <v>3.130138997188492</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07881859441977267</v>
+        <v>0.09385659695440438</v>
       </c>
       <c r="P11" t="n">
-        <v>4.003888853002715</v>
+        <v>60.90456090561772</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3544504618834986</v>
+        <v>0.4229533708268262</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3248493550269912</v>
+        <v>0.1961008959773403</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01651603235086502</v>
+        <v>0.002117966700986179</v>
       </c>
       <c r="T11" t="n">
-        <v>5.593409956630178</v>
+        <v>64.23080079878356</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4492126552509194</v>
+        <v>0.4574958216980837</v>
       </c>
       <c r="V11" t="n">
-        <v>179.5480752440816</v>
+        <v>15.56937934229981</v>
       </c>
       <c r="W11" t="n">
-        <v>14.32668124018072</v>
+        <v>0.1105031992553645</v>
       </c>
       <c r="X11" t="n">
-        <v>9.297200759251913</v>
+        <v>59.40397461255392</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.8016723146283045</v>
+        <v>0.6606717077982324</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.1112223696369393</v>
+        <v>0.5360344423209259</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.8912537790574629</v>
+        <v>1.262026816875109</v>
       </c>
       <c r="AB11" t="n">
-        <v>-6.234260968080661</v>
+        <v>3.410139308625479</v>
       </c>
     </row>
     <row r="12">
@@ -6333,73 +6333,73 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757188</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818113</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660924</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.291705223267642</v>
+        <v>2.718886951404886</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08089882716378545</v>
+        <v>0.4815885544145599</v>
       </c>
       <c r="P12" t="n">
-        <v>4.141069375116669</v>
+        <v>61.28982167991393</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4666293863881644</v>
+        <v>0.6437673253075923</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3287270493738142</v>
+        <v>0.1953174385555001</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01627368551985351</v>
+        <v>0.001379213896457038</v>
       </c>
       <c r="T12" t="n">
-        <v>5.761501647758126</v>
+        <v>64.20402606987432</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5632070078141208</v>
+        <v>0.2213109058245358</v>
       </c>
       <c r="V12" t="n">
-        <v>174.7178585323764</v>
+        <v>15.57547053551403</v>
       </c>
       <c r="W12" t="n">
-        <v>17.69515513596162</v>
+        <v>0.05365524225775704</v>
       </c>
       <c r="X12" t="n">
-        <v>9.579611221949259</v>
+        <v>59.28412262598673</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.8504041861205341</v>
+        <v>0.5010737911191746</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.2147071912094278</v>
+        <v>0.942463913868157</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.2428359197714576</v>
+        <v>1.012786003052116</v>
       </c>
       <c r="AB12" t="n">
-        <v>-8.756754395212505</v>
+        <v>3.450596357361341</v>
       </c>
     </row>
     <row r="13">
@@ -6427,73 +6427,73 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8366387179945584</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.9235417287411419</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416777</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.273206406041578</v>
+        <v>3.084528051404671</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04377367211860447</v>
+        <v>0.1277287731654614</v>
       </c>
       <c r="P13" t="n">
-        <v>4.226664143777406</v>
+        <v>62.07660985541878</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3308915886694174</v>
+        <v>0.2054515466693488</v>
       </c>
       <c r="R13" t="n">
-        <v>0.323663271100884</v>
+        <v>0.1970441405613468</v>
       </c>
       <c r="S13" t="n">
-        <v>0.005544551874649938</v>
+        <v>0.00046641075640512</v>
       </c>
       <c r="T13" t="n">
-        <v>5.823533820919867</v>
+        <v>65.3581820473848</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3751709323693725</v>
+        <v>0.2414832094330966</v>
       </c>
       <c r="V13" t="n">
-        <v>172.1961559852246</v>
+        <v>15.30044242337567</v>
       </c>
       <c r="W13" t="n">
-        <v>11.16301990987927</v>
+        <v>0.05653395056725858</v>
       </c>
       <c r="X13" t="n">
-        <v>9.59859307607015</v>
+        <v>60.66661739349365</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.504151454420004</v>
+        <v>0.1368778697374766</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.759239789119267</v>
+        <v>1.490807866174425</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.93796172305524</v>
+        <v>2.002068621107012</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.07366799972161</v>
+        <v>1.623889282870116</v>
       </c>
     </row>
     <row r="14">
@@ -6521,73 +6521,73 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.8526107293020054</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.846616077472835</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.779266846434712</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.198697713640052</v>
+        <v>3.147603802807841</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04588698018089579</v>
+        <v>0.2858501525158395</v>
       </c>
       <c r="P14" t="n">
-        <v>3.791752829721121</v>
+        <v>62.62943875421558</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4513562730217205</v>
+        <v>0.807629141541976</v>
       </c>
       <c r="R14" t="n">
-        <v>0.328459926089979</v>
+        <v>0.1924473698781766</v>
       </c>
       <c r="S14" t="n">
-        <v>0.007710985860745694</v>
+        <v>0.0001658623182433698</v>
       </c>
       <c r="T14" t="n">
-        <v>5.318910469451152</v>
+        <v>65.9694899269016</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5037417138936777</v>
+        <v>1.05217026570697</v>
       </c>
       <c r="V14" t="n">
-        <v>189.0894238198177</v>
+        <v>15.16108460988195</v>
       </c>
       <c r="W14" t="n">
-        <v>17.12854250288773</v>
+        <v>0.2409656019529471</v>
       </c>
       <c r="X14" t="n">
-        <v>9.128423690795898</v>
+        <v>61.0341280301412</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6301827530281828</v>
+        <v>0.6590904370528601</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.08762347630109</v>
+        <v>2.525741423710154</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.764059995204061</v>
+        <v>3.867732821782958</v>
       </c>
       <c r="AB14" t="n">
-        <v>-1.251464024427327</v>
+        <v>0.6982897075564065</v>
       </c>
     </row>
     <row r="15">
@@ -6615,73 +6615,73 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.728604791515712</v>
+        <v>0.7149502064942949</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.244322522499686</v>
+        <v>3.235233858635618</v>
       </c>
       <c r="O15" t="n">
-        <v>0.06976887124935006</v>
+        <v>0.1714013747493033</v>
       </c>
       <c r="P15" t="n">
-        <v>3.922959594782729</v>
+        <v>64.50529935341301</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4561247068948571</v>
+        <v>1.308210807478819</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3306975646797312</v>
+        <v>0.1957951481963537</v>
       </c>
       <c r="S15" t="n">
-        <v>0.02461973069973277</v>
+        <v>0.005125253734806239</v>
       </c>
       <c r="T15" t="n">
-        <v>5.497979681962146</v>
+        <v>67.93632836024499</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5486390187645549</v>
+        <v>1.477580139081936</v>
       </c>
       <c r="V15" t="n">
-        <v>183.1573852046965</v>
+        <v>14.72425285512592</v>
       </c>
       <c r="W15" t="n">
-        <v>19.13912458950384</v>
+        <v>0.3164076682736837</v>
       </c>
       <c r="X15" t="n">
-        <v>9.108398040135702</v>
+        <v>62.95878370602926</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.9068367328362542</v>
+        <v>1.040507951231618</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.6040203031693</v>
+        <v>16.9326354540477</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.40248385313634</v>
+        <v>22.84776121827268</v>
       </c>
       <c r="AB15" t="n">
-        <v>-4.349364037872652</v>
+        <v>-2.203099719768055</v>
       </c>
     </row>
     <row r="16">
@@ -6709,73 +6709,73 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.240890381119375</v>
+        <v>3.07401487108204</v>
       </c>
       <c r="O16" t="n">
-        <v>0.02291066127572707</v>
+        <v>0.03963301017321692</v>
       </c>
       <c r="P16" t="n">
-        <v>4.036811780340313</v>
+        <v>61.68362194618701</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.1936570828221393</v>
+        <v>2.622065695103189</v>
       </c>
       <c r="R16" t="n">
-        <v>0.343587698396542</v>
+        <v>0.1885085064330554</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02059602669422076</v>
+        <v>0.00197565656885907</v>
       </c>
       <c r="T16" t="n">
-        <v>5.621289859856229</v>
+        <v>64.94614532370211</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2304245714581085</v>
+        <v>2.65850857002784</v>
       </c>
       <c r="V16" t="n">
-        <v>178.0962129130423</v>
+        <v>15.41419372853648</v>
       </c>
       <c r="W16" t="n">
-        <v>7.360652628863341</v>
+        <v>0.6163978293862388</v>
       </c>
       <c r="X16" t="n">
-        <v>9.47118059794108</v>
+        <v>60.12889409065247</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.3487614145643093</v>
+        <v>2.789103668801163</v>
       </c>
       <c r="Z16" t="n">
-        <v>44.25163758881126</v>
+        <v>38.0518920578551</v>
       </c>
       <c r="AA16" t="n">
-        <v>53.69159129775718</v>
+        <v>49.80363132446787</v>
       </c>
       <c r="AB16" t="n">
-        <v>-6.99246984476975</v>
+        <v>2.379413190060116</v>
       </c>
     </row>
     <row r="17">
@@ -6803,64 +6803,64 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177132</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.195114706416027</v>
+        <v>3.459603306828011</v>
       </c>
       <c r="O17" t="n">
-        <v>0.07245072200281331</v>
+        <v>0.1029811123327936</v>
       </c>
       <c r="P17" t="n">
-        <v>3.739857279515308</v>
+        <v>62.76951731043979</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4305006474917559</v>
+        <v>0.8454500031771921</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3214192212893919</v>
+        <v>0.19619194899422</v>
       </c>
       <c r="S17" t="n">
-        <v>0.02057036352137559</v>
+        <v>0.00259606394817039</v>
       </c>
       <c r="T17" t="n">
-        <v>5.256391207220727</v>
+        <v>66.42531256626202</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5182114893728951</v>
+        <v>0.8007284624570832</v>
       </c>
       <c r="V17" t="n">
-        <v>191.4857997151397</v>
+        <v>15.0559504574627</v>
       </c>
       <c r="W17" t="n">
-        <v>18.91563971862029</v>
+        <v>0.1802392310244327</v>
       </c>
       <c r="X17" t="n">
-        <v>8.783390124638876</v>
+        <v>60.83974011739095</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.8521905829646145</v>
+        <v>0.9823820398093274</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
